--- a/exports/trend_1d/COCHINSHIP_full_report.xlsx
+++ b/exports/trend_1d/COCHINSHIP_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>14.96</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43083</v>
+        <v>43084</v>
       </c>
       <c r="H2" t="n">
-        <v>271</v>
+        <v>268.4</v>
       </c>
       <c r="I2" t="n">
         <v>270.5704059693488</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K2" t="n">
-        <v>7.5</v>
+        <v>6.47</v>
       </c>
       <c r="L2" t="n">
         <v>0.24</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.9</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H3" t="n">
-        <v>256</v>
+        <v>258.7</v>
       </c>
       <c r="I3" t="n">
         <v>258.1495621216674</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K3" t="n">
-        <v>4.62</v>
+        <v>3.61</v>
       </c>
       <c r="L3" t="n">
         <v>6.18</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>5.89</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43230</v>
+        <v>43231</v>
       </c>
       <c r="H4" t="n">
-        <v>257.15</v>
+        <v>251.9</v>
       </c>
       <c r="I4" t="n">
         <v>254.120511498878</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6</v>
+        <v>-2.63</v>
       </c>
       <c r="L4" t="n">
-        <v>1.14</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
         <v>0.64</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.96</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43314</v>
+        <v>43315</v>
       </c>
       <c r="H5" t="n">
-        <v>226.9</v>
+        <v>228.9</v>
       </c>
       <c r="I5" t="n">
         <v>227.6086070523528</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K5" t="n">
-        <v>9.92</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>3.06</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>5.95</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43335</v>
+        <v>43336</v>
       </c>
       <c r="H6" t="n">
-        <v>217</v>
+        <v>214.05</v>
       </c>
       <c r="I6" t="n">
         <v>215.2740783787168</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.2</v>
+        <v>-6.49</v>
       </c>
       <c r="L6" t="n">
-        <v>5.5</v>
+        <v>6.64</v>
       </c>
       <c r="M6" t="n">
         <v>2.99</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43385</v>
+        <v>43388</v>
       </c>
       <c r="H7" t="n">
-        <v>197.6</v>
+        <v>200.95</v>
       </c>
       <c r="I7" t="n">
         <v>200.8230127039186</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K7" t="n">
-        <v>7.69</v>
+        <v>6.12</v>
       </c>
       <c r="L7" t="n">
         <v>2.31</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>9.92</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43472</v>
+        <v>43473</v>
       </c>
       <c r="H8" t="n">
-        <v>182.8</v>
+        <v>182.3</v>
       </c>
       <c r="I8" t="n">
         <v>182.4294974343989</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.029999999999999</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>9.18</v>
+        <v>9.93</v>
       </c>
       <c r="M8" t="n">
         <v>1.22</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.33</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43524</v>
+        <v>43525</v>
       </c>
       <c r="H9" t="n">
-        <v>174.5</v>
+        <v>181.9</v>
       </c>
       <c r="I9" t="n">
         <v>180.2685643981759</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K9" t="n">
-        <v>4.28</v>
+        <v>0.22</v>
       </c>
       <c r="L9" t="n">
         <v>3.95</v>
@@ -954,7 +1061,7 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>4.24</v>
       </c>
       <c r="O9" t="n">
         <v>-0.27</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.66</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H10" t="n">
-        <v>185.8</v>
+        <v>182.8</v>
       </c>
       <c r="I10" t="n">
         <v>185.5021730728899</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K10" t="n">
-        <v>2.14</v>
+        <v>0.49</v>
       </c>
       <c r="L10" t="n">
         <v>3.85</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>7.62</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43613</v>
+        <v>43614</v>
       </c>
       <c r="H11" t="n">
-        <v>188</v>
+        <v>190.6</v>
       </c>
       <c r="I11" t="n">
         <v>189.1760392726753</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.84</v>
+        <v>-4.27</v>
       </c>
       <c r="L11" t="n">
-        <v>5.91</v>
+        <v>6.51</v>
       </c>
       <c r="M11" t="n">
         <v>4.6</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>7.85</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43663</v>
+        <v>43664</v>
       </c>
       <c r="H12" t="n">
-        <v>183</v>
+        <v>181.8</v>
       </c>
       <c r="I12" t="n">
         <v>182.5709367309196</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.99</v>
+        <v>-4.62</v>
       </c>
       <c r="L12" t="n">
-        <v>4.2</v>
+        <v>4.77</v>
       </c>
       <c r="M12" t="n">
         <v>1.14</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.11</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43720</v>
+        <v>43721</v>
       </c>
       <c r="H13" t="n">
-        <v>176.7</v>
+        <v>180.9</v>
       </c>
       <c r="I13" t="n">
         <v>179.4550086050316</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K13" t="n">
-        <v>2.81</v>
+        <v>0.5</v>
       </c>
       <c r="L13" t="n">
         <v>2.09</v>
@@ -1182,7 +1337,7 @@
         <v>1.61</v>
       </c>
       <c r="N13" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="O13" t="n">
         <v>-0.66</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>7.86</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43739</v>
+        <v>43741</v>
       </c>
       <c r="H14" t="n">
-        <v>167.8</v>
+        <v>166.1</v>
       </c>
       <c r="I14" t="n">
         <v>166.6767206505569</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.24</v>
+        <v>-8.18</v>
       </c>
       <c r="L14" t="n">
         <v>9.07</v>
       </c>
       <c r="M14" t="n">
-        <v>-0</v>
+        <v>1.34</v>
       </c>
       <c r="N14" t="n">
         <v>2.68</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>8.58</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43761</v>
+        <v>43762</v>
       </c>
       <c r="H15" t="n">
-        <v>169.9</v>
+        <v>178.8</v>
       </c>
       <c r="I15" t="n">
         <v>176.3681852957108</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.29</v>
+        <v>-7.65</v>
       </c>
       <c r="L15" t="n">
-        <v>6.62</v>
+        <v>8.31</v>
       </c>
       <c r="M15" t="n">
         <v>1.75</v>
       </c>
       <c r="N15" t="n">
-        <v>2.49</v>
+        <v>5.24</v>
       </c>
       <c r="O15" t="n">
         <v>-1.01</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.76</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43852</v>
+        <v>43853</v>
       </c>
       <c r="H16" t="n">
-        <v>212.9</v>
+        <v>201.8</v>
       </c>
       <c r="I16" t="n">
         <v>206.5388312439139</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K16" t="n">
-        <v>19.07</v>
+        <v>12.86</v>
       </c>
       <c r="L16" t="n">
         <v>4.59</v>
@@ -1353,7 +1544,7 @@
         <v>1.81</v>
       </c>
       <c r="N16" t="n">
-        <v>3.24</v>
+        <v>5.21</v>
       </c>
       <c r="O16" t="n">
         <v>5.24</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>14.66</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43987</v>
+        <v>43990</v>
       </c>
       <c r="H17" t="n">
-        <v>121.7</v>
+        <v>132.9</v>
       </c>
       <c r="I17" t="n">
         <v>125.0080363065948</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K17" t="n">
-        <v>39.69</v>
+        <v>34.14</v>
       </c>
       <c r="L17" t="n">
         <v>6.05</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>15.82</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44074</v>
+        <v>44075</v>
       </c>
       <c r="H18" t="n">
-        <v>166.3</v>
+        <v>164.9</v>
       </c>
       <c r="I18" t="n">
         <v>165.9341877925887</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K18" t="n">
-        <v>25.13</v>
+        <v>24.08</v>
       </c>
       <c r="L18" t="n">
         <v>7.3</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>13.89</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44125</v>
+        <v>44126</v>
       </c>
       <c r="H19" t="n">
-        <v>163.45</v>
+        <v>179.8</v>
       </c>
       <c r="I19" t="n">
         <v>172.7915393704385</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K19" t="n">
-        <v>0.88</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>6.25</v>
+        <v>12.19</v>
       </c>
       <c r="M19" t="n">
-        <v>1.95</v>
+        <v>4.62</v>
       </c>
       <c r="N19" t="n">
-        <v>4.59</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
         <v>-0.84</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>13.21</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H20" t="n">
-        <v>179.7</v>
+        <v>176.1</v>
       </c>
       <c r="I20" t="n">
         <v>179.6662742914287</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.06</v>
+        <v>-2.06</v>
       </c>
       <c r="L20" t="n">
         <v>7.68</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>10.71</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44249</v>
+        <v>44250</v>
       </c>
       <c r="H21" t="n">
-        <v>176.5</v>
+        <v>190.2</v>
       </c>
       <c r="I21" t="n">
         <v>187.1683067741993</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.23</v>
+        <v>-8.01</v>
       </c>
       <c r="L21" t="n">
-        <v>6.1</v>
+        <v>11.87</v>
       </c>
       <c r="M21" t="n">
         <v>1.43</v>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>7.76</v>
       </c>
       <c r="O21" t="n">
         <v>-2</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>13.32</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H22" t="n">
-        <v>178.1</v>
+        <v>175.6</v>
       </c>
       <c r="I22" t="n">
         <v>175.952144454435</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.36</v>
+        <v>-7.68</v>
       </c>
       <c r="L22" t="n">
-        <v>8.52</v>
+        <v>8.68</v>
       </c>
       <c r="M22" t="n">
         <v>1.12</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>10.98</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44328</v>
+        <v>44330</v>
       </c>
       <c r="H23" t="n">
-        <v>188.2</v>
+        <v>191.7</v>
       </c>
       <c r="I23" t="n">
         <v>190.2670536005369</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.18</v>
+        <v>-9.17</v>
       </c>
       <c r="L23" t="n">
-        <v>9.34</v>
+        <v>10.19</v>
       </c>
       <c r="M23" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="N23" t="n">
         <v>4.35</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44393</v>
+        <v>44396</v>
       </c>
       <c r="H24" t="n">
-        <v>192.15</v>
+        <v>190.35</v>
       </c>
       <c r="I24" t="n">
         <v>190.7403512099458</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K24" t="n">
-        <v>0.23</v>
+        <v>-0.7</v>
       </c>
       <c r="L24" t="n">
         <v>2.35</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44452</v>
+        <v>44453</v>
       </c>
       <c r="H25" t="n">
-        <v>183.5</v>
+        <v>187.55</v>
       </c>
       <c r="I25" t="n">
         <v>186.7759020261534</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>1.47</v>
       </c>
       <c r="L25" t="n">
         <v>1.52</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>7.64</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H26" t="n">
-        <v>178.1</v>
+        <v>175.3</v>
       </c>
       <c r="I26" t="n">
         <v>175.8643037445281</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.04</v>
+        <v>-6.53</v>
       </c>
       <c r="L26" t="n">
-        <v>6.42</v>
+        <v>7.06</v>
       </c>
       <c r="M26" t="n">
         <v>0.43</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44510</v>
+        <v>44511</v>
       </c>
       <c r="H27" t="n">
-        <v>182.2</v>
+        <v>187.05</v>
       </c>
       <c r="I27" t="n">
         <v>186.5633342337882</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.94</v>
+        <v>-6.7</v>
       </c>
       <c r="L27" t="n">
-        <v>6.96</v>
+        <v>7.67</v>
       </c>
       <c r="M27" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>1.56</v>
+        <v>2.66</v>
       </c>
       <c r="O27" t="n">
         <v>-1.57</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>8.23</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44526</v>
+        <v>44529</v>
       </c>
       <c r="H28" t="n">
-        <v>174.6</v>
+        <v>171.2</v>
       </c>
       <c r="I28" t="n">
         <v>174.4521362570837</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.66</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>7.11</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>1.35</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44559</v>
+        <v>44560</v>
       </c>
       <c r="H29" t="n">
-        <v>172.8</v>
+        <v>178.3</v>
       </c>
       <c r="I29" t="n">
         <v>176.1595699848417</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.93</v>
+        <v>-4.15</v>
       </c>
       <c r="L29" t="n">
-        <v>2.72</v>
+        <v>5.14</v>
       </c>
       <c r="M29" t="n">
         <v>0.75</v>
       </c>
       <c r="N29" t="n">
-        <v>2.1</v>
+        <v>3.18</v>
       </c>
       <c r="O29" t="n">
         <v>-1.95</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>8.23</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H30" t="n">
-        <v>172.5</v>
+        <v>167.4</v>
       </c>
       <c r="I30" t="n">
         <v>167.4644715891179</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.25</v>
+        <v>-6.11</v>
       </c>
       <c r="L30" t="n">
-        <v>4.32</v>
+        <v>6.62</v>
       </c>
       <c r="M30" t="n">
         <v>-0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="O30" t="n">
         <v>3.18</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.42</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H31" t="n">
-        <v>151.4</v>
+        <v>158.9</v>
       </c>
       <c r="I31" t="n">
         <v>154.1028864289487</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K31" t="n">
-        <v>9.56</v>
+        <v>5.08</v>
       </c>
       <c r="L31" t="n">
         <v>3.94</v>
@@ -2208,7 +2579,7 @@
         <v>1.99</v>
       </c>
       <c r="N31" t="n">
-        <v>2.92</v>
+        <v>4.95</v>
       </c>
       <c r="O31" t="n">
         <v>-2.96</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>9.26</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H32" t="n">
-        <v>157.85</v>
+        <v>152.15</v>
       </c>
       <c r="I32" t="n">
         <v>156.4079497522634</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.66</v>
+        <v>-4.25</v>
       </c>
       <c r="L32" t="n">
-        <v>4.09</v>
+        <v>5.29</v>
       </c>
       <c r="M32" t="n">
         <v>1.47</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>13.56</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44701</v>
+        <v>44704</v>
       </c>
       <c r="H33" t="n">
-        <v>161.9</v>
+        <v>171.55</v>
       </c>
       <c r="I33" t="n">
         <v>170.987082575977</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.41</v>
+        <v>-12.75</v>
       </c>
       <c r="L33" t="n">
-        <v>9.369999999999999</v>
+        <v>14.99</v>
       </c>
       <c r="M33" t="n">
-        <v>2.11</v>
+        <v>3.77</v>
       </c>
       <c r="N33" t="n">
-        <v>3.93</v>
+        <v>5.96</v>
       </c>
       <c r="O33" t="n">
         <v>-3.61</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>12.71</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H34" t="n">
-        <v>299</v>
+        <v>272.1</v>
       </c>
       <c r="I34" t="n">
         <v>289.9700734782569</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K34" t="n">
-        <v>74.29000000000001</v>
+        <v>58.61</v>
       </c>
       <c r="L34" t="n">
         <v>13.44</v>
@@ -2379,7 +2786,7 @@
         <v>1.52</v>
       </c>
       <c r="N34" t="n">
-        <v>7.02</v>
+        <v>9</v>
       </c>
       <c r="O34" t="n">
         <v>5.96</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>8</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>22.09</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45014</v>
+        <v>45016</v>
       </c>
       <c r="H35" t="n">
-        <v>229.5</v>
+        <v>237.9</v>
       </c>
       <c r="I35" t="n">
         <v>234.7384027476932</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K35" t="n">
-        <v>15.66</v>
+        <v>12.57</v>
       </c>
       <c r="L35" t="n">
         <v>11.8</v>
       </c>
       <c r="M35" t="n">
-        <v>1.31</v>
+        <v>5.9</v>
       </c>
       <c r="N35" t="n">
         <v>11.23</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>12.12</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45065</v>
+        <v>45068</v>
       </c>
       <c r="H36" t="n">
-        <v>271.1</v>
+        <v>242.9</v>
       </c>
       <c r="I36" t="n">
         <v>251.8705407750965</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K36" t="n">
-        <v>13.96</v>
+        <v>2.1</v>
       </c>
       <c r="L36" t="n">
         <v>1.93</v>
       </c>
       <c r="M36" t="n">
-        <v>0.35</v>
+        <v>10.37</v>
       </c>
       <c r="N36" t="n">
-        <v>3.59</v>
+        <v>10.4</v>
       </c>
       <c r="O36" t="n">
         <v>3.66</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>13.01</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45079</v>
+        <v>45082</v>
       </c>
       <c r="H37" t="n">
-        <v>250.65</v>
+        <v>279.45</v>
       </c>
       <c r="I37" t="n">
         <v>265.8672500709478</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.19</v>
+        <v>-15.05</v>
       </c>
       <c r="L37" t="n">
-        <v>4.57</v>
+        <v>18.36</v>
       </c>
       <c r="M37" t="n">
         <v>0.74</v>
       </c>
       <c r="N37" t="n">
-        <v>1.63</v>
+        <v>11.49</v>
       </c>
       <c r="O37" t="n">
         <v>-10.4</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>16.14</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45190</v>
+        <v>45191</v>
       </c>
       <c r="H38" t="n">
-        <v>519.4</v>
+        <v>501.1</v>
       </c>
       <c r="I38" t="n">
         <v>515.9769311284617</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K38" t="n">
-        <v>85.87</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="L38" t="n">
         <v>11.04</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>21.24</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45243</v>
+        <v>45245</v>
       </c>
       <c r="H39" t="n">
-        <v>526.9</v>
+        <v>549.1</v>
       </c>
       <c r="I39" t="n">
         <v>535.6313334602771</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.15</v>
+        <v>-9.58</v>
       </c>
       <c r="L39" t="n">
         <v>12.75</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.81</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H40" t="n">
-        <v>818.05</v>
+        <v>730.8</v>
       </c>
       <c r="I40" t="n">
         <v>790.8316469721738</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K40" t="n">
-        <v>48.98</v>
+        <v>33.09</v>
       </c>
       <c r="L40" t="n">
         <v>4.32</v>
@@ -2721,7 +3200,7 @@
         <v>3.89</v>
       </c>
       <c r="N40" t="n">
-        <v>8.75</v>
+        <v>10.67</v>
       </c>
       <c r="O40" t="n">
         <v>4.21</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>22.65</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45372</v>
+        <v>45373</v>
       </c>
       <c r="H41" t="n">
-        <v>895.85</v>
+        <v>902.45</v>
       </c>
       <c r="I41" t="n">
         <v>896.2999489514611</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K41" t="n">
-        <v>-22.58</v>
+        <v>-23.49</v>
       </c>
       <c r="L41" t="n">
-        <v>26.29</v>
+        <v>27.37</v>
       </c>
       <c r="M41" t="n">
         <v>1.25</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>14.46</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H42" t="n">
-        <v>2411</v>
+        <v>2290.45</v>
       </c>
       <c r="I42" t="n">
         <v>2394.378344938843</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K42" t="n">
-        <v>167.16</v>
+        <v>153.8</v>
       </c>
       <c r="L42" t="n">
         <v>4.15</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>6</v>
+      </c>
+      <c r="U42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>21.18</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H43" t="n">
-        <v>1432.45</v>
+        <v>1504.05</v>
       </c>
       <c r="I43" t="n">
         <v>1467.907095269887</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K43" t="n">
-        <v>37.46</v>
+        <v>34.33</v>
       </c>
       <c r="L43" t="n">
         <v>8.76</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>13.89</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H44" t="n">
-        <v>1493.55</v>
+        <v>1466.9</v>
       </c>
       <c r="I44" t="n">
         <v>1490.865630483467</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.7</v>
+        <v>-2.47</v>
       </c>
       <c r="L44" t="n">
-        <v>2.93</v>
+        <v>3.99</v>
       </c>
       <c r="M44" t="n">
         <v>3.11</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>14.16</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H45" t="n">
-        <v>1340.9</v>
+        <v>1456.7</v>
       </c>
       <c r="I45" t="n">
         <v>1423.960275631636</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K45" t="n">
-        <v>8.59</v>
+        <v>0.7</v>
       </c>
       <c r="L45" t="n">
         <v>10.43</v>
@@ -3006,7 +3545,7 @@
         <v>2.4</v>
       </c>
       <c r="N45" t="n">
-        <v>5.21</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="O45" t="n">
         <v>-1.78</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>16.47</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="H46" t="n">
-        <v>2091.2</v>
+        <v>2044.2</v>
       </c>
       <c r="I46" t="n">
         <v>2059.017717243094</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K46" t="n">
-        <v>43.56</v>
+        <v>40.33</v>
       </c>
       <c r="L46" t="n">
         <v>15.94</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>18.32</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="H47" t="n">
-        <v>1745.7</v>
+        <v>1807.8</v>
       </c>
       <c r="I47" t="n">
         <v>1769.326952450997</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K47" t="n">
-        <v>14.6</v>
+        <v>11.56</v>
       </c>
       <c r="L47" t="n">
         <v>4.04</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>11.17</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H48" t="n">
-        <v>1768.7</v>
+        <v>1702.7</v>
       </c>
       <c r="I48" t="n">
         <v>1750.633308419684</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.16</v>
+        <v>-5.81</v>
       </c>
       <c r="L48" t="n">
-        <v>3.2</v>
+        <v>6.05</v>
       </c>
       <c r="M48" t="n">
         <v>0.34</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.15</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="H49" t="n">
-        <v>1548.3</v>
+        <v>1666.3</v>
       </c>
       <c r="I49" t="n">
         <v>1617.368465014609</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K49" t="n">
-        <v>9.07</v>
+        <v>2.14</v>
       </c>
       <c r="L49" t="n">
         <v>6.01</v>
@@ -3234,7 +3821,7 @@
         <v>0.85</v>
       </c>
       <c r="N49" t="n">
-        <v>2.8</v>
+        <v>7.62</v>
       </c>
       <c r="O49" t="n">
         <v>-3.73</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>11.99</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="H50" t="n">
-        <v>1526.6</v>
+        <v>1506.4</v>
       </c>
       <c r="I50" t="n">
         <v>1523.870088593523</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K50" t="n">
-        <v>-8.380000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="L50" t="n">
-        <v>8.77</v>
+        <v>9.92</v>
       </c>
       <c r="M50" t="n">
-        <v>0.26</v>
+        <v>0.96</v>
       </c>
       <c r="N50" t="n">
         <v>1.73</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="H51" t="n">
-        <v>1523.1</v>
+        <v>1622.9</v>
       </c>
       <c r="I51" t="n">
         <v>1588.977261217745</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.11</v>
+        <v>-7.73</v>
       </c>
       <c r="L51" t="n">
-        <v>2.55</v>
+        <v>8.34</v>
       </c>
       <c r="M51" t="n">
         <v>0.6</v>
       </c>
       <c r="N51" t="n">
-        <v>2.33</v>
+        <v>6.55</v>
       </c>
       <c r="O51" t="n">
         <v>-1.32</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>13.02</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H52" t="n">
-        <v>1491.7</v>
+        <v>1448.9</v>
       </c>
       <c r="I52" t="n">
         <v>1461.915762023534</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K52" t="n">
-        <v>-8.08</v>
+        <v>-10.72</v>
       </c>
       <c r="L52" t="n">
-        <v>10.35</v>
+        <v>11.99</v>
       </c>
       <c r="M52" t="n">
-        <v>0.63</v>
+        <v>3.8</v>
       </c>
       <c r="N52" t="n">
         <v>6.34</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>12.05</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="H53" t="n">
-        <v>1379.8</v>
+        <v>1423.9</v>
       </c>
       <c r="I53" t="n">
         <v>1421.566713129477</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K53" t="n">
-        <v>4.77</v>
+        <v>1.73</v>
       </c>
       <c r="L53" t="n">
         <v>5.21</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>15.91</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="H54" t="n">
-        <v>1645.2</v>
+        <v>1594.5</v>
       </c>
       <c r="I54" t="n">
         <v>1608.95945040334</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>15.54</v>
+        <v>11.98</v>
       </c>
       <c r="L54" t="n">
         <v>3.61</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>14.29</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="H55" t="n">
-        <v>1425</v>
+        <v>1490</v>
       </c>
       <c r="I55" t="n">
         <v>1484.244766957608</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K55" t="n">
-        <v>10.63</v>
+        <v>6.55</v>
       </c>
       <c r="L55" t="n">
         <v>3.42</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H56" t="n">
-        <v>1520.4</v>
+        <v>1381</v>
       </c>
       <c r="I56" t="n">
         <v>1449.076029645492</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K56" t="n">
-        <v>2.04</v>
+        <v>-7.32</v>
       </c>
       <c r="L56" t="n">
-        <v>4.93</v>
+        <v>7.92</v>
       </c>
       <c r="M56" t="n">
         <v>3.11</v>
       </c>
       <c r="N56" t="n">
-        <v>2.59</v>
+        <v>9.17</v>
       </c>
       <c r="O56" t="n">
         <v>4.56</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3693,6 +4376,14 @@
       <c r="Q57" t="n">
         <v>31</v>
       </c>
+      <c r="R57" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7597,7 +8288,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -7607,7 +8298,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -7617,7 +8308,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8">
@@ -7627,7 +8318,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -7637,7 +8328,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -7647,7 +8338,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109.2</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="11">
@@ -7657,7 +8348,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -7667,7 +8358,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -7677,7 +8368,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.9</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="14">
@@ -7687,7 +8378,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.29</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="15">
@@ -7697,7 +8388,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.65</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="16">
@@ -7707,7 +8398,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.74</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="17">
@@ -7717,7 +8408,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>167.16</v>
+        <v>153.8</v>
       </c>
     </row>
     <row r="18">
@@ -7727,7 +8418,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.7</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="19">
@@ -7737,7 +8428,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.33</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="20">
@@ -7747,7 +8438,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.5</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="21">
@@ -7757,7 +8448,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.29</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="22">
@@ -7767,7 +8458,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -7777,7 +8468,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -7787,7 +8478,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="25">
@@ -7807,7 +8498,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.8</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="27">
@@ -7827,7 +8518,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
